--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Slovenia PrvaLiga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Slovenia PrvaLiga_20242025.xlsx
@@ -7721,7 +7721,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>7483705</v>
+        <v>7483707</v>
       </c>
       <c r="C34" t="s">
         <v>68</v>
@@ -7736,10 +7736,10 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -7751,175 +7751,175 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M34">
         <v>0</v>
       </c>
       <c r="N34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O34" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="P34" t="s">
         <v>81</v>
       </c>
       <c r="Q34">
-        <v>1.92</v>
+        <v>3.75</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>6.41</v>
+        <v>2.64</v>
       </c>
       <c r="T34">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="U34">
-        <v>3.29</v>
+        <v>3.06</v>
       </c>
       <c r="V34">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="W34">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X34">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z34">
-        <v>1.43</v>
+        <v>2.9</v>
       </c>
       <c r="AA34">
-        <v>4.08</v>
+        <v>3.3</v>
       </c>
       <c r="AB34">
-        <v>6.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
         <v>1.01</v>
       </c>
       <c r="AD34">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="AG34">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH34">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AI34">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AJ34">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AK34">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="AL34">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AM34">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="AN34">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AP34">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="AR34">
-        <v>2.01</v>
+        <v>1.21</v>
       </c>
       <c r="AS34">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT34">
-        <v>3.59</v>
+        <v>2.62</v>
       </c>
       <c r="AU34">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AV34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AX34">
         <v>6</v>
       </c>
       <c r="AY34">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ34">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BB34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC34">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD34">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="BE34">
-        <v>11</v>
+        <v>6.25</v>
       </c>
       <c r="BF34">
-        <v>5.56</v>
+        <v>1.94</v>
       </c>
       <c r="BG34">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="BH34">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="BI34">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BJ34">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="BK34">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="BL34">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="BM34">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="BN34">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="BO34">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="BP34">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="35" spans="1:68">
@@ -7927,7 +7927,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>7483707</v>
+        <v>7483705</v>
       </c>
       <c r="C35" t="s">
         <v>68</v>
@@ -7942,10 +7942,10 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -7957,175 +7957,175 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="P35" t="s">
         <v>81</v>
       </c>
       <c r="Q35">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>2.64</v>
+        <v>6.41</v>
       </c>
       <c r="T35">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="U35">
-        <v>3.06</v>
+        <v>3.29</v>
       </c>
       <c r="V35">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="W35">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Y35">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>2.9</v>
+        <v>1.43</v>
       </c>
       <c r="AA35">
-        <v>3.3</v>
+        <v>4.08</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>6.12</v>
       </c>
       <c r="AC35">
         <v>1.01</v>
       </c>
       <c r="AD35">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AE35">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="AG35">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH35">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AI35">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AJ35">
+        <v>1.83</v>
+      </c>
+      <c r="AK35">
+        <v>1.12</v>
+      </c>
+      <c r="AL35">
+        <v>1.18</v>
+      </c>
+      <c r="AM35">
+        <v>2.15</v>
+      </c>
+      <c r="AN35">
+        <v>2.33</v>
+      </c>
+      <c r="AO35">
+        <v>1.5</v>
+      </c>
+      <c r="AP35">
+        <v>2</v>
+      </c>
+      <c r="AQ35">
+        <v>0.89</v>
+      </c>
+      <c r="AR35">
         <v>2.01</v>
       </c>
-      <c r="AK35">
-        <v>1.66</v>
-      </c>
-      <c r="AL35">
-        <v>1.27</v>
-      </c>
-      <c r="AM35">
-        <v>1.3</v>
-      </c>
-      <c r="AN35">
-        <v>1.5</v>
-      </c>
-      <c r="AO35">
-        <v>0.5</v>
-      </c>
-      <c r="AP35">
-        <v>1.67</v>
-      </c>
-      <c r="AQ35">
-        <v>1.33</v>
-      </c>
-      <c r="AR35">
-        <v>1.21</v>
-      </c>
       <c r="AS35">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AT35">
-        <v>2.62</v>
+        <v>3.59</v>
       </c>
       <c r="AU35">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AV35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX35">
         <v>6</v>
       </c>
       <c r="AY35">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AZ35">
+        <v>10</v>
+      </c>
+      <c r="BA35">
+        <v>7</v>
+      </c>
+      <c r="BB35">
+        <v>2</v>
+      </c>
+      <c r="BC35">
+        <v>9</v>
+      </c>
+      <c r="BD35">
+        <v>1.22</v>
+      </c>
+      <c r="BE35">
         <v>11</v>
       </c>
-      <c r="BA35">
+      <c r="BF35">
+        <v>5.56</v>
+      </c>
+      <c r="BG35">
+        <v>1.18</v>
+      </c>
+      <c r="BH35">
+        <v>4.33</v>
+      </c>
+      <c r="BI35">
+        <v>1.33</v>
+      </c>
+      <c r="BJ35">
         <v>3</v>
       </c>
-      <c r="BB35">
-        <v>3</v>
-      </c>
-      <c r="BC35">
-        <v>6</v>
-      </c>
-      <c r="BD35">
-        <v>2.26</v>
-      </c>
-      <c r="BE35">
-        <v>6.25</v>
-      </c>
-      <c r="BF35">
-        <v>1.94</v>
-      </c>
-      <c r="BG35">
-        <v>1.3</v>
-      </c>
-      <c r="BH35">
-        <v>3.2</v>
-      </c>
-      <c r="BI35">
-        <v>1.46</v>
-      </c>
-      <c r="BJ35">
-        <v>2.45</v>
-      </c>
       <c r="BK35">
-        <v>1.81</v>
+        <v>1.52</v>
       </c>
       <c r="BL35">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="BM35">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="BN35">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="BO35">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="BP35">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="36" spans="1:68">
@@ -10193,7 +10193,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>7483723</v>
+        <v>7483721</v>
       </c>
       <c r="C46" t="s">
         <v>68</v>
@@ -10208,160 +10208,160 @@
         <v>10</v>
       </c>
       <c r="G46" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="s">
         <v>81</v>
       </c>
       <c r="P46" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z46">
-        <v>8.699999999999999</v>
+        <v>3.47</v>
       </c>
       <c r="AA46">
-        <v>5.15</v>
+        <v>3.55</v>
       </c>
       <c r="AB46">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AG46">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH46">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN46">
         <v>1.5</v>
       </c>
       <c r="AO46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP46">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="AQ46">
-        <v>2.33</v>
+        <v>0.89</v>
       </c>
       <c r="AR46">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AS46">
-        <v>1.81</v>
+        <v>1.37</v>
       </c>
       <c r="AT46">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AU46">
+        <v>4</v>
+      </c>
+      <c r="AV46">
         <v>3</v>
       </c>
-      <c r="AV46">
-        <v>4</v>
-      </c>
       <c r="AW46">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AX46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY46">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AZ46">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA46">
         <v>5</v>
       </c>
       <c r="BB46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD46">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BE46">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF46">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BG46">
         <v>0</v>
@@ -10376,22 +10376,22 @@
         <v>0</v>
       </c>
       <c r="BK46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BL46">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BM46">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BN46">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BO46">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BP46">
-        <v>0</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="47" spans="1:68">
@@ -10399,7 +10399,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>7483721</v>
+        <v>7483723</v>
       </c>
       <c r="C47" t="s">
         <v>68</v>
@@ -10414,160 +10414,160 @@
         <v>10</v>
       </c>
       <c r="G47" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" t="s">
         <v>81</v>
       </c>
       <c r="P47" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="Q47">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>3.47</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA47">
-        <v>3.55</v>
+        <v>5.15</v>
       </c>
       <c r="AB47">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC47">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH47">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AI47">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL47">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AM47">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN47">
         <v>1.5</v>
       </c>
       <c r="AO47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP47">
-        <v>0.89</v>
+        <v>1.44</v>
       </c>
       <c r="AQ47">
-        <v>0.89</v>
+        <v>2.33</v>
       </c>
       <c r="AR47">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AS47">
-        <v>1.37</v>
+        <v>1.81</v>
       </c>
       <c r="AT47">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="AU47">
+        <v>3</v>
+      </c>
+      <c r="AV47">
         <v>4</v>
       </c>
-      <c r="AV47">
+      <c r="AW47">
         <v>3</v>
       </c>
-      <c r="AW47">
+      <c r="AX47">
+        <v>3</v>
+      </c>
+      <c r="AY47">
+        <v>6</v>
+      </c>
+      <c r="AZ47">
         <v>7</v>
-      </c>
-      <c r="AX47">
-        <v>6</v>
-      </c>
-      <c r="AY47">
-        <v>12</v>
-      </c>
-      <c r="AZ47">
-        <v>10</v>
       </c>
       <c r="BA47">
         <v>5</v>
       </c>
       <c r="BB47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC47">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD47">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BE47">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BF47">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -10582,22 +10582,22 @@
         <v>0</v>
       </c>
       <c r="BK47">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BL47">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BM47">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BN47">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BO47">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BP47">
-        <v>1.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:68">
